--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_292_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_292_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X19" t="n">
         <v>4</v>
@@ -1923,10 +1923,10 @@
         <v>30</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3295,16 +3295,16 @@
         <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>107</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X30" t="n">
         <v>28</v>
@@ -4292,10 +4292,10 @@
         <v>10</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4488,7 +4488,7 @@
         <v>8</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4687,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>4</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5468,7 +5468,7 @@
         <v>6</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>6</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -5866,10 +5866,10 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X43" t="n">
         <v>2</v>
@@ -6392,16 +6392,16 @@
         <v>79</v>
       </c>
       <c r="T46" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X46" t="n">
         <v>33</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_292_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_292_EL.xlsx
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P2" t="n">
         <v>5</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>75.68</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
         <v>4</v>
@@ -851,20 +851,20 @@
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>82.50</t>
+          <t>65.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1739,14 +1739,14 @@
         <v>3</v>
       </c>
       <c r="X19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y19" t="n">
         <v>4</v>
       </c>
-      <c r="Y19" t="n">
-        <v>6</v>
-      </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y20" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2131,10 +2131,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y26" t="n">
         <v>4</v>
       </c>
-      <c r="Y26" t="n">
-        <v>5</v>
-      </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3839,14 +3839,14 @@
         <v>4</v>
       </c>
       <c r="X30" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="Y30" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4729,25 +4729,25 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5088,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -5480,10 +5480,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5712,18 +5712,18 @@
         <v>2</v>
       </c>
       <c r="AH42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ42" t="n">
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
@@ -5872,14 +5872,14 @@
         <v>2</v>
       </c>
       <c r="X43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6068,10 +6068,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6404,14 +6404,14 @@
         <v>3</v>
       </c>
       <c r="X46" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="Y46" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6437,25 +6437,25 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
